--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludwin/Elektronik/abr/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE438A0-64B4-4D4B-9701-80239C370359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A55B96-2558-3D40-911C-E85E28B36A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="680" windowWidth="28240" windowHeight="16980" xr2:uid="{41CB2213-D8A7-9E4C-B8DD-9C8DFC4D30CF}"/>
   </bookViews>
@@ -799,10 +799,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5052CC5-C330-E244-B58A-6FE7387F9BB1}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="48.5" customWidth="1"/>
+    <col min="2" max="2" width="48.5" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1266,6 +1270,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="53" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludwin/Elektronik/abr/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A55B96-2558-3D40-911C-E85E28B36A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FD1F03-FED2-CD4C-8558-E30680D817FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="680" windowWidth="28240" windowHeight="16980" xr2:uid="{41CB2213-D8A7-9E4C-B8DD-9C8DFC4D30CF}"/>
   </bookViews>
@@ -1270,6 +1270,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="53" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="67" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>